--- a/data/availability/projects/tatweer-misr/il-monte-galala.xlsx
+++ b/data/availability/projects/tatweer-misr/il-monte-galala.xlsx
@@ -654,7 +654,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -704,7 +704,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -904,7 +904,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C20" t="n">
@@ -1809,7 +1809,6 @@
       <c r="G2" t="n">
         <v>70</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1866,7 +1865,6 @@
       <c r="G3" t="n">
         <v>70</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1923,7 +1921,6 @@
       <c r="G4" t="n">
         <v>175</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -1980,7 +1977,6 @@
       <c r="G5" t="n">
         <v>175</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2037,7 +2033,6 @@
       <c r="G6" t="n">
         <v>175</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2070,7 +2065,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2094,7 +2089,6 @@
       <c r="G7" t="n">
         <v>446</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2127,7 +2121,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2151,7 +2145,6 @@
       <c r="G8" t="n">
         <v>288</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2184,7 +2177,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -2208,7 +2201,6 @@
       <c r="G9" t="n">
         <v>248</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2241,7 +2233,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2265,7 +2257,6 @@
       <c r="G10" t="n">
         <v>288</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2322,7 +2313,6 @@
       <c r="G11" t="n">
         <v>160</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2355,7 +2345,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2379,7 +2369,6 @@
       <c r="G12" t="n">
         <v>263</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2436,7 +2425,6 @@
       <c r="G13" t="n">
         <v>110</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2493,7 +2481,6 @@
       <c r="G14" t="n">
         <v>115</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2550,7 +2537,6 @@
       <c r="G15" t="n">
         <v>115</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2607,7 +2593,6 @@
       <c r="G16" t="n">
         <v>95</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2664,7 +2649,6 @@
       <c r="G17" t="n">
         <v>115</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2721,7 +2705,6 @@
       <c r="G18" t="n">
         <v>95</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2778,7 +2761,6 @@
       <c r="G19" t="n">
         <v>115</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2835,7 +2817,6 @@
       <c r="G20" t="n">
         <v>95</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2892,7 +2873,6 @@
       <c r="G21" t="n">
         <v>70</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -2949,7 +2929,6 @@
       <c r="G22" t="n">
         <v>115</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3006,7 +2985,6 @@
       <c r="G23" t="n">
         <v>95</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3063,7 +3041,6 @@
       <c r="G24" t="n">
         <v>95</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3120,7 +3097,6 @@
       <c r="G25" t="n">
         <v>115</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3177,7 +3153,6 @@
       <c r="G26" t="n">
         <v>95</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3234,7 +3209,6 @@
       <c r="G27" t="n">
         <v>95</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3291,7 +3265,6 @@
       <c r="G28" t="n">
         <v>115</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3348,7 +3321,6 @@
       <c r="G29" t="n">
         <v>140</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3405,7 +3377,6 @@
       <c r="G30" t="n">
         <v>140</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3462,7 +3433,6 @@
       <c r="G31" t="n">
         <v>140</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3519,7 +3489,6 @@
       <c r="G32" t="n">
         <v>140</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3576,7 +3545,6 @@
       <c r="G33" t="n">
         <v>140</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3633,7 +3601,6 @@
       <c r="G34" t="n">
         <v>140</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3690,7 +3657,6 @@
       <c r="G35" t="n">
         <v>140</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3747,7 +3713,6 @@
       <c r="G36" t="n">
         <v>140</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3804,7 +3769,6 @@
       <c r="G37" t="n">
         <v>140</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3861,7 +3825,6 @@
       <c r="G38" t="n">
         <v>140</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3918,7 +3881,6 @@
       <c r="G39" t="n">
         <v>140</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -3951,7 +3913,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -3975,7 +3937,6 @@
       <c r="G40" t="n">
         <v>155</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4008,7 +3969,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4032,7 +3993,6 @@
       <c r="G41" t="n">
         <v>155</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4065,7 +4025,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4089,7 +4049,6 @@
       <c r="G42" t="n">
         <v>155</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4122,7 +4081,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4146,7 +4105,6 @@
       <c r="G43" t="n">
         <v>155</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4179,7 +4137,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4203,7 +4161,6 @@
       <c r="G44" t="n">
         <v>155</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4236,7 +4193,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4260,7 +4217,6 @@
       <c r="G45" t="n">
         <v>155</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4293,7 +4249,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4317,7 +4273,6 @@
       <c r="G46" t="n">
         <v>170</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4350,7 +4305,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -4374,7 +4329,6 @@
       <c r="G47" t="n">
         <v>170</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4407,7 +4361,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4431,7 +4385,6 @@
       <c r="G48" t="n">
         <v>170</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4464,7 +4417,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4488,7 +4441,6 @@
       <c r="G49" t="n">
         <v>170</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4521,7 +4473,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4545,7 +4497,6 @@
       <c r="G50" t="n">
         <v>170</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4578,7 +4529,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4602,7 +4553,6 @@
       <c r="G51" t="n">
         <v>170</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4635,7 +4585,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4659,7 +4609,6 @@
       <c r="G52" t="n">
         <v>155</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4692,7 +4641,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -4716,7 +4665,6 @@
       <c r="G53" t="n">
         <v>155</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4749,7 +4697,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4773,7 +4721,6 @@
       <c r="G54" t="n">
         <v>155</v>
       </c>
-      <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4806,7 +4753,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -4830,7 +4777,6 @@
       <c r="G55" t="n">
         <v>155</v>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4863,7 +4809,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4887,7 +4833,6 @@
       <c r="G56" t="n">
         <v>155</v>
       </c>
-      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -4920,7 +4865,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4944,7 +4889,6 @@
       <c r="G57" t="n">
         <v>155</v>
       </c>
-      <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5001,7 +4945,6 @@
       <c r="G58" t="n">
         <v>140</v>
       </c>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5058,7 +5001,6 @@
       <c r="G59" t="n">
         <v>140</v>
       </c>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5115,7 +5057,6 @@
       <c r="G60" t="n">
         <v>140</v>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5172,7 +5113,6 @@
       <c r="G61" t="n">
         <v>140</v>
       </c>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5229,7 +5169,6 @@
       <c r="G62" t="n">
         <v>140</v>
       </c>
-      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5286,7 +5225,6 @@
       <c r="G63" t="n">
         <v>140</v>
       </c>
-      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5343,7 +5281,6 @@
       <c r="G64" t="n">
         <v>140</v>
       </c>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5400,7 +5337,6 @@
       <c r="G65" t="n">
         <v>140</v>
       </c>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5433,7 +5369,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -5457,7 +5393,6 @@
       <c r="G66" t="n">
         <v>155</v>
       </c>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5490,7 +5425,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -5514,7 +5449,6 @@
       <c r="G67" t="n">
         <v>155</v>
       </c>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5547,7 +5481,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -5571,7 +5505,6 @@
       <c r="G68" t="n">
         <v>155</v>
       </c>
-      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5604,7 +5537,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -5628,7 +5561,6 @@
       <c r="G69" t="n">
         <v>155</v>
       </c>
-      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5661,7 +5593,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -5685,7 +5617,6 @@
       <c r="G70" t="n">
         <v>155</v>
       </c>
-      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5718,7 +5649,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -5742,7 +5673,6 @@
       <c r="G71" t="n">
         <v>155</v>
       </c>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5775,7 +5705,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -5799,7 +5729,6 @@
       <c r="G72" t="n">
         <v>155</v>
       </c>
-      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5832,7 +5761,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -5856,7 +5785,6 @@
       <c r="G73" t="n">
         <v>155</v>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5913,7 +5841,6 @@
       <c r="G74" t="n">
         <v>140</v>
       </c>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -5970,7 +5897,6 @@
       <c r="G75" t="n">
         <v>140</v>
       </c>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6027,7 +5953,6 @@
       <c r="G76" t="n">
         <v>140</v>
       </c>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6084,7 +6009,6 @@
       <c r="G77" t="n">
         <v>140</v>
       </c>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6117,7 +6041,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -6141,7 +6065,6 @@
       <c r="G78" t="n">
         <v>50</v>
       </c>
-      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6174,7 +6097,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -6198,7 +6121,6 @@
       <c r="G79" t="n">
         <v>50</v>
       </c>
-      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6231,7 +6153,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -6255,7 +6177,6 @@
       <c r="G80" t="n">
         <v>50</v>
       </c>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6288,7 +6209,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -6312,7 +6233,6 @@
       <c r="G81" t="n">
         <v>50</v>
       </c>
-      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6345,7 +6265,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -6369,7 +6289,6 @@
       <c r="G82" t="n">
         <v>50</v>
       </c>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6402,7 +6321,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -6426,7 +6345,6 @@
       <c r="G83" t="n">
         <v>50</v>
       </c>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6459,7 +6377,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -6483,7 +6401,6 @@
       <c r="G84" t="n">
         <v>50</v>
       </c>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6516,7 +6433,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -6540,7 +6457,6 @@
       <c r="G85" t="n">
         <v>50</v>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6573,7 +6489,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -6597,7 +6513,6 @@
       <c r="G86" t="n">
         <v>50</v>
       </c>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6630,7 +6545,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -6654,7 +6569,6 @@
       <c r="G87" t="n">
         <v>50</v>
       </c>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6687,7 +6601,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -6711,7 +6625,6 @@
       <c r="G88" t="n">
         <v>50</v>
       </c>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6744,7 +6657,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -6768,7 +6681,6 @@
       <c r="G89" t="n">
         <v>50</v>
       </c>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6801,7 +6713,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -6825,7 +6737,6 @@
       <c r="G90" t="n">
         <v>50</v>
       </c>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6858,7 +6769,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -6882,7 +6793,6 @@
       <c r="G91" t="n">
         <v>50</v>
       </c>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6915,7 +6825,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -6939,7 +6849,6 @@
       <c r="G92" t="n">
         <v>50</v>
       </c>
-      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -6972,7 +6881,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -6996,7 +6905,6 @@
       <c r="G93" t="n">
         <v>50</v>
       </c>
-      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7029,7 +6937,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -7053,7 +6961,6 @@
       <c r="G94" t="n">
         <v>50</v>
       </c>
-      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7086,7 +6993,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -7110,7 +7017,6 @@
       <c r="G95" t="n">
         <v>50</v>
       </c>
-      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7143,7 +7049,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -7167,7 +7073,6 @@
       <c r="G96" t="n">
         <v>50</v>
       </c>
-      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7200,7 +7105,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -7224,7 +7129,6 @@
       <c r="G97" t="n">
         <v>50</v>
       </c>
-      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7257,7 +7161,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -7281,7 +7185,6 @@
       <c r="G98" t="n">
         <v>50</v>
       </c>
-      <c r="H98" t="inlineStr"/>
       <c r="I98" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7314,7 +7217,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -7338,7 +7241,6 @@
       <c r="G99" t="n">
         <v>50</v>
       </c>
-      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7371,7 +7273,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -7395,7 +7297,6 @@
       <c r="G100" t="n">
         <v>50</v>
       </c>
-      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7428,7 +7329,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -7452,7 +7353,6 @@
       <c r="G101" t="n">
         <v>50</v>
       </c>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7485,7 +7385,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -7509,7 +7409,6 @@
       <c r="G102" t="n">
         <v>50</v>
       </c>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7542,7 +7441,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -7566,7 +7465,6 @@
       <c r="G103" t="n">
         <v>50</v>
       </c>
-      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7599,7 +7497,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -7623,7 +7521,6 @@
       <c r="G104" t="n">
         <v>50</v>
       </c>
-      <c r="H104" t="inlineStr"/>
       <c r="I104" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7656,7 +7553,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -7680,7 +7577,6 @@
       <c r="G105" t="n">
         <v>50</v>
       </c>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7713,7 +7609,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -7737,7 +7633,6 @@
       <c r="G106" t="n">
         <v>50</v>
       </c>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7770,7 +7665,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -7794,7 +7689,6 @@
       <c r="G107" t="n">
         <v>50</v>
       </c>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7827,7 +7721,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -7851,7 +7745,6 @@
       <c r="G108" t="n">
         <v>50</v>
       </c>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7884,7 +7777,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -7908,7 +7801,6 @@
       <c r="G109" t="n">
         <v>50</v>
       </c>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7941,7 +7833,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -7965,7 +7857,6 @@
       <c r="G110" t="n">
         <v>50</v>
       </c>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -7998,7 +7889,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -8022,7 +7913,6 @@
       <c r="G111" t="n">
         <v>50</v>
       </c>
-      <c r="H111" t="inlineStr"/>
       <c r="I111" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8055,7 +7945,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -8079,7 +7969,6 @@
       <c r="G112" t="n">
         <v>50</v>
       </c>
-      <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8112,7 +8001,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -8136,7 +8025,6 @@
       <c r="G113" t="n">
         <v>50</v>
       </c>
-      <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8169,7 +8057,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -8193,7 +8081,6 @@
       <c r="G114" t="n">
         <v>50</v>
       </c>
-      <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8226,7 +8113,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -8250,7 +8137,6 @@
       <c r="G115" t="n">
         <v>50</v>
       </c>
-      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8283,7 +8169,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -8307,7 +8193,6 @@
       <c r="G116" t="n">
         <v>50</v>
       </c>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8340,7 +8225,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -8364,7 +8249,6 @@
       <c r="G117" t="n">
         <v>50</v>
       </c>
-      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8397,7 +8281,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -8421,7 +8305,6 @@
       <c r="G118" t="n">
         <v>50</v>
       </c>
-      <c r="H118" t="inlineStr"/>
       <c r="I118" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8454,7 +8337,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -8478,7 +8361,6 @@
       <c r="G119" t="n">
         <v>50</v>
       </c>
-      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8511,7 +8393,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -8535,7 +8417,6 @@
       <c r="G120" t="n">
         <v>50</v>
       </c>
-      <c r="H120" t="inlineStr"/>
       <c r="I120" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8568,7 +8449,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -8592,7 +8473,6 @@
       <c r="G121" t="n">
         <v>50</v>
       </c>
-      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8625,7 +8505,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -8649,7 +8529,6 @@
       <c r="G122" t="n">
         <v>50</v>
       </c>
-      <c r="H122" t="inlineStr"/>
       <c r="I122" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8682,7 +8561,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -8706,7 +8585,6 @@
       <c r="G123" t="n">
         <v>50</v>
       </c>
-      <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8739,7 +8617,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -8763,7 +8641,6 @@
       <c r="G124" t="n">
         <v>50</v>
       </c>
-      <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8796,7 +8673,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -8820,7 +8697,6 @@
       <c r="G125" t="n">
         <v>50</v>
       </c>
-      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8853,7 +8729,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -8877,7 +8753,6 @@
       <c r="G126" t="n">
         <v>50</v>
       </c>
-      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8910,7 +8785,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -8934,7 +8809,6 @@
       <c r="G127" t="n">
         <v>50</v>
       </c>
-      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -8967,7 +8841,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -8991,7 +8865,6 @@
       <c r="G128" t="n">
         <v>50</v>
       </c>
-      <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9024,7 +8897,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -9048,7 +8921,6 @@
       <c r="G129" t="n">
         <v>50</v>
       </c>
-      <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9081,7 +8953,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -9105,7 +8977,6 @@
       <c r="G130" t="n">
         <v>50</v>
       </c>
-      <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9138,7 +9009,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -9162,7 +9033,6 @@
       <c r="G131" t="n">
         <v>50</v>
       </c>
-      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9195,7 +9065,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -9219,7 +9089,6 @@
       <c r="G132" t="n">
         <v>50</v>
       </c>
-      <c r="H132" t="inlineStr"/>
       <c r="I132" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9252,7 +9121,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -9276,7 +9145,6 @@
       <c r="G133" t="n">
         <v>50</v>
       </c>
-      <c r="H133" t="inlineStr"/>
       <c r="I133" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9309,7 +9177,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -9333,7 +9201,6 @@
       <c r="G134" t="n">
         <v>50</v>
       </c>
-      <c r="H134" t="inlineStr"/>
       <c r="I134" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9366,7 +9233,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -9390,7 +9257,6 @@
       <c r="G135" t="n">
         <v>50</v>
       </c>
-      <c r="H135" t="inlineStr"/>
       <c r="I135" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9423,7 +9289,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -9447,7 +9313,6 @@
       <c r="G136" t="n">
         <v>50</v>
       </c>
-      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9480,7 +9345,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -9504,7 +9369,6 @@
       <c r="G137" t="n">
         <v>50</v>
       </c>
-      <c r="H137" t="inlineStr"/>
       <c r="I137" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9537,7 +9401,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -9561,7 +9425,6 @@
       <c r="G138" t="n">
         <v>50</v>
       </c>
-      <c r="H138" t="inlineStr"/>
       <c r="I138" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9594,7 +9457,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -9618,7 +9481,6 @@
       <c r="G139" t="n">
         <v>50</v>
       </c>
-      <c r="H139" t="inlineStr"/>
       <c r="I139" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9651,7 +9513,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -9675,7 +9537,6 @@
       <c r="G140" t="n">
         <v>50</v>
       </c>
-      <c r="H140" t="inlineStr"/>
       <c r="I140" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9708,7 +9569,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -9732,7 +9593,6 @@
       <c r="G141" t="n">
         <v>50</v>
       </c>
-      <c r="H141" t="inlineStr"/>
       <c r="I141" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9765,7 +9625,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -9789,7 +9649,6 @@
       <c r="G142" t="n">
         <v>50</v>
       </c>
-      <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9822,7 +9681,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -9846,7 +9705,6 @@
       <c r="G143" t="n">
         <v>50</v>
       </c>
-      <c r="H143" t="inlineStr"/>
       <c r="I143" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9879,7 +9737,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -9903,7 +9761,6 @@
       <c r="G144" t="n">
         <v>50</v>
       </c>
-      <c r="H144" t="inlineStr"/>
       <c r="I144" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9936,7 +9793,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -9960,7 +9817,6 @@
       <c r="G145" t="n">
         <v>50</v>
       </c>
-      <c r="H145" t="inlineStr"/>
       <c r="I145" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -9993,7 +9849,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -10017,7 +9873,6 @@
       <c r="G146" t="n">
         <v>50</v>
       </c>
-      <c r="H146" t="inlineStr"/>
       <c r="I146" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10050,7 +9905,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -10074,7 +9929,6 @@
       <c r="G147" t="n">
         <v>50</v>
       </c>
-      <c r="H147" t="inlineStr"/>
       <c r="I147" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10107,7 +9961,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -10131,7 +9985,6 @@
       <c r="G148" t="n">
         <v>50</v>
       </c>
-      <c r="H148" t="inlineStr"/>
       <c r="I148" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10164,7 +10017,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -10188,7 +10041,6 @@
       <c r="G149" t="n">
         <v>50</v>
       </c>
-      <c r="H149" t="inlineStr"/>
       <c r="I149" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10221,7 +10073,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -10245,7 +10097,6 @@
       <c r="G150" t="n">
         <v>50</v>
       </c>
-      <c r="H150" t="inlineStr"/>
       <c r="I150" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10278,7 +10129,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -10302,7 +10153,6 @@
       <c r="G151" t="n">
         <v>50</v>
       </c>
-      <c r="H151" t="inlineStr"/>
       <c r="I151" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10359,7 +10209,6 @@
       <c r="G152" t="n">
         <v>70</v>
       </c>
-      <c r="H152" t="inlineStr"/>
       <c r="I152" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10416,7 +10265,6 @@
       <c r="G153" t="n">
         <v>105</v>
       </c>
-      <c r="H153" t="inlineStr"/>
       <c r="I153" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10473,7 +10321,6 @@
       <c r="G154" t="n">
         <v>105</v>
       </c>
-      <c r="H154" t="inlineStr"/>
       <c r="I154" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10530,7 +10377,6 @@
       <c r="G155" t="n">
         <v>70</v>
       </c>
-      <c r="H155" t="inlineStr"/>
       <c r="I155" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10587,7 +10433,6 @@
       <c r="G156" t="n">
         <v>70</v>
       </c>
-      <c r="H156" t="inlineStr"/>
       <c r="I156" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10644,7 +10489,6 @@
       <c r="G157" t="n">
         <v>90</v>
       </c>
-      <c r="H157" t="inlineStr"/>
       <c r="I157" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10701,7 +10545,6 @@
       <c r="G158" t="n">
         <v>105</v>
       </c>
-      <c r="H158" t="inlineStr"/>
       <c r="I158" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10758,7 +10601,6 @@
       <c r="G159" t="n">
         <v>105</v>
       </c>
-      <c r="H159" t="inlineStr"/>
       <c r="I159" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10815,7 +10657,6 @@
       <c r="G160" t="n">
         <v>70</v>
       </c>
-      <c r="H160" t="inlineStr"/>
       <c r="I160" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10872,7 +10713,6 @@
       <c r="G161" t="n">
         <v>70</v>
       </c>
-      <c r="H161" t="inlineStr"/>
       <c r="I161" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10929,7 +10769,6 @@
       <c r="G162" t="n">
         <v>65</v>
       </c>
-      <c r="H162" t="inlineStr"/>
       <c r="I162" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -10986,7 +10825,6 @@
       <c r="G163" t="n">
         <v>105</v>
       </c>
-      <c r="H163" t="inlineStr"/>
       <c r="I163" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11043,7 +10881,6 @@
       <c r="G164" t="n">
         <v>105</v>
       </c>
-      <c r="H164" t="inlineStr"/>
       <c r="I164" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11100,7 +10937,6 @@
       <c r="G165" t="n">
         <v>70</v>
       </c>
-      <c r="H165" t="inlineStr"/>
       <c r="I165" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11157,7 +10993,6 @@
       <c r="G166" t="n">
         <v>90</v>
       </c>
-      <c r="H166" t="inlineStr"/>
       <c r="I166" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11214,7 +11049,6 @@
       <c r="G167" t="n">
         <v>105</v>
       </c>
-      <c r="H167" t="inlineStr"/>
       <c r="I167" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11271,7 +11105,6 @@
       <c r="G168" t="n">
         <v>105</v>
       </c>
-      <c r="H168" t="inlineStr"/>
       <c r="I168" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11328,7 +11161,6 @@
       <c r="G169" t="n">
         <v>70</v>
       </c>
-      <c r="H169" t="inlineStr"/>
       <c r="I169" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11385,7 +11217,6 @@
       <c r="G170" t="n">
         <v>70</v>
       </c>
-      <c r="H170" t="inlineStr"/>
       <c r="I170" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11442,7 +11273,6 @@
       <c r="G171" t="n">
         <v>105</v>
       </c>
-      <c r="H171" t="inlineStr"/>
       <c r="I171" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11499,7 +11329,6 @@
       <c r="G172" t="n">
         <v>105</v>
       </c>
-      <c r="H172" t="inlineStr"/>
       <c r="I172" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11556,7 +11385,6 @@
       <c r="G173" t="n">
         <v>70</v>
       </c>
-      <c r="H173" t="inlineStr"/>
       <c r="I173" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11613,7 +11441,6 @@
       <c r="G174" t="n">
         <v>70</v>
       </c>
-      <c r="H174" t="inlineStr"/>
       <c r="I174" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11670,7 +11497,6 @@
       <c r="G175" t="n">
         <v>65</v>
       </c>
-      <c r="H175" t="inlineStr"/>
       <c r="I175" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11727,7 +11553,6 @@
       <c r="G176" t="n">
         <v>90</v>
       </c>
-      <c r="H176" t="inlineStr"/>
       <c r="I176" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11784,7 +11609,6 @@
       <c r="G177" t="n">
         <v>105</v>
       </c>
-      <c r="H177" t="inlineStr"/>
       <c r="I177" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11841,7 +11665,6 @@
       <c r="G178" t="n">
         <v>105</v>
       </c>
-      <c r="H178" t="inlineStr"/>
       <c r="I178" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11898,7 +11721,6 @@
       <c r="G179" t="n">
         <v>105</v>
       </c>
-      <c r="H179" t="inlineStr"/>
       <c r="I179" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -11955,7 +11777,6 @@
       <c r="G180" t="n">
         <v>105</v>
       </c>
-      <c r="H180" t="inlineStr"/>
       <c r="I180" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12012,7 +11833,6 @@
       <c r="G181" t="n">
         <v>70</v>
       </c>
-      <c r="H181" t="inlineStr"/>
       <c r="I181" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12069,7 +11889,6 @@
       <c r="G182" t="n">
         <v>70</v>
       </c>
-      <c r="H182" t="inlineStr"/>
       <c r="I182" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12126,7 +11945,6 @@
       <c r="G183" t="n">
         <v>90</v>
       </c>
-      <c r="H183" t="inlineStr"/>
       <c r="I183" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12183,7 +12001,6 @@
       <c r="G184" t="n">
         <v>105</v>
       </c>
-      <c r="H184" t="inlineStr"/>
       <c r="I184" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12240,7 +12057,6 @@
       <c r="G185" t="n">
         <v>105</v>
       </c>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12297,7 +12113,6 @@
       <c r="G186" t="n">
         <v>105</v>
       </c>
-      <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12354,7 +12169,6 @@
       <c r="G187" t="n">
         <v>90</v>
       </c>
-      <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12411,7 +12225,6 @@
       <c r="G188" t="n">
         <v>105</v>
       </c>
-      <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12468,7 +12281,6 @@
       <c r="G189" t="n">
         <v>105</v>
       </c>
-      <c r="H189" t="inlineStr"/>
       <c r="I189" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12525,7 +12337,6 @@
       <c r="G190" t="n">
         <v>105</v>
       </c>
-      <c r="H190" t="inlineStr"/>
       <c r="I190" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12582,7 +12393,6 @@
       <c r="G191" t="n">
         <v>115</v>
       </c>
-      <c r="H191" t="inlineStr"/>
       <c r="I191" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12639,7 +12449,6 @@
       <c r="G192" t="n">
         <v>115</v>
       </c>
-      <c r="H192" t="inlineStr"/>
       <c r="I192" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12696,7 +12505,6 @@
       <c r="G193" t="n">
         <v>70</v>
       </c>
-      <c r="H193" t="inlineStr"/>
       <c r="I193" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12753,7 +12561,6 @@
       <c r="G194" t="n">
         <v>70</v>
       </c>
-      <c r="H194" t="inlineStr"/>
       <c r="I194" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12810,7 +12617,6 @@
       <c r="G195" t="n">
         <v>70</v>
       </c>
-      <c r="H195" t="inlineStr"/>
       <c r="I195" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12867,7 +12673,6 @@
       <c r="G196" t="n">
         <v>115</v>
       </c>
-      <c r="H196" t="inlineStr"/>
       <c r="I196" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12924,7 +12729,6 @@
       <c r="G197" t="n">
         <v>70</v>
       </c>
-      <c r="H197" t="inlineStr"/>
       <c r="I197" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -12981,7 +12785,6 @@
       <c r="G198" t="n">
         <v>70</v>
       </c>
-      <c r="H198" t="inlineStr"/>
       <c r="I198" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13038,7 +12841,6 @@
       <c r="G199" t="n">
         <v>95</v>
       </c>
-      <c r="H199" t="inlineStr"/>
       <c r="I199" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13095,7 +12897,6 @@
       <c r="G200" t="n">
         <v>95</v>
       </c>
-      <c r="H200" t="inlineStr"/>
       <c r="I200" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13152,7 +12953,6 @@
       <c r="G201" t="n">
         <v>95</v>
       </c>
-      <c r="H201" t="inlineStr"/>
       <c r="I201" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13209,7 +13009,6 @@
       <c r="G202" t="n">
         <v>95</v>
       </c>
-      <c r="H202" t="inlineStr"/>
       <c r="I202" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13266,7 +13065,6 @@
       <c r="G203" t="n">
         <v>95</v>
       </c>
-      <c r="H203" t="inlineStr"/>
       <c r="I203" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13323,7 +13121,6 @@
       <c r="G204" t="n">
         <v>95</v>
       </c>
-      <c r="H204" t="inlineStr"/>
       <c r="I204" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13380,7 +13177,6 @@
       <c r="G205" t="n">
         <v>155</v>
       </c>
-      <c r="H205" t="inlineStr"/>
       <c r="I205" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13437,7 +13233,6 @@
       <c r="G206" t="n">
         <v>155</v>
       </c>
-      <c r="H206" t="inlineStr"/>
       <c r="I206" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13494,7 +13289,6 @@
       <c r="G207" t="n">
         <v>155</v>
       </c>
-      <c r="H207" t="inlineStr"/>
       <c r="I207" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13551,7 +13345,6 @@
       <c r="G208" t="n">
         <v>155</v>
       </c>
-      <c r="H208" t="inlineStr"/>
       <c r="I208" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13608,7 +13401,6 @@
       <c r="G209" t="n">
         <v>155</v>
       </c>
-      <c r="H209" t="inlineStr"/>
       <c r="I209" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13665,7 +13457,6 @@
       <c r="G210" t="n">
         <v>130</v>
       </c>
-      <c r="H210" t="inlineStr"/>
       <c r="I210" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13722,7 +13513,6 @@
       <c r="G211" t="n">
         <v>130</v>
       </c>
-      <c r="H211" t="inlineStr"/>
       <c r="I211" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13779,7 +13569,6 @@
       <c r="G212" t="n">
         <v>130</v>
       </c>
-      <c r="H212" t="inlineStr"/>
       <c r="I212" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13836,7 +13625,6 @@
       <c r="G213" t="n">
         <v>130</v>
       </c>
-      <c r="H213" t="inlineStr"/>
       <c r="I213" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13893,7 +13681,6 @@
       <c r="G214" t="n">
         <v>130</v>
       </c>
-      <c r="H214" t="inlineStr"/>
       <c r="I214" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -13950,7 +13737,6 @@
       <c r="G215" t="n">
         <v>130</v>
       </c>
-      <c r="H215" t="inlineStr"/>
       <c r="I215" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14007,7 +13793,6 @@
       <c r="G216" t="n">
         <v>130</v>
       </c>
-      <c r="H216" t="inlineStr"/>
       <c r="I216" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14064,7 +13849,6 @@
       <c r="G217" t="n">
         <v>130</v>
       </c>
-      <c r="H217" t="inlineStr"/>
       <c r="I217" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14121,7 +13905,6 @@
       <c r="G218" t="n">
         <v>130</v>
       </c>
-      <c r="H218" t="inlineStr"/>
       <c r="I218" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14178,7 +13961,6 @@
       <c r="G219" t="n">
         <v>130</v>
       </c>
-      <c r="H219" t="inlineStr"/>
       <c r="I219" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14235,7 +14017,6 @@
       <c r="G220" t="n">
         <v>130</v>
       </c>
-      <c r="H220" t="inlineStr"/>
       <c r="I220" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14292,7 +14073,6 @@
       <c r="G221" t="n">
         <v>130</v>
       </c>
-      <c r="H221" t="inlineStr"/>
       <c r="I221" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14349,7 +14129,6 @@
       <c r="G222" t="n">
         <v>130</v>
       </c>
-      <c r="H222" t="inlineStr"/>
       <c r="I222" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14406,7 +14185,6 @@
       <c r="G223" t="n">
         <v>130</v>
       </c>
-      <c r="H223" t="inlineStr"/>
       <c r="I223" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14463,7 +14241,6 @@
       <c r="G224" t="n">
         <v>130</v>
       </c>
-      <c r="H224" t="inlineStr"/>
       <c r="I224" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14520,7 +14297,6 @@
       <c r="G225" t="n">
         <v>130</v>
       </c>
-      <c r="H225" t="inlineStr"/>
       <c r="I225" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14577,7 +14353,6 @@
       <c r="G226" t="n">
         <v>130</v>
       </c>
-      <c r="H226" t="inlineStr"/>
       <c r="I226" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14634,7 +14409,6 @@
       <c r="G227" t="n">
         <v>130</v>
       </c>
-      <c r="H227" t="inlineStr"/>
       <c r="I227" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14691,7 +14465,6 @@
       <c r="G228" t="n">
         <v>130</v>
       </c>
-      <c r="H228" t="inlineStr"/>
       <c r="I228" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14748,7 +14521,6 @@
       <c r="G229" t="n">
         <v>130</v>
       </c>
-      <c r="H229" t="inlineStr"/>
       <c r="I229" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14805,7 +14577,6 @@
       <c r="G230" t="n">
         <v>130</v>
       </c>
-      <c r="H230" t="inlineStr"/>
       <c r="I230" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14862,7 +14633,6 @@
       <c r="G231" t="n">
         <v>130</v>
       </c>
-      <c r="H231" t="inlineStr"/>
       <c r="I231" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14919,7 +14689,6 @@
       <c r="G232" t="n">
         <v>130</v>
       </c>
-      <c r="H232" t="inlineStr"/>
       <c r="I232" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -14976,7 +14745,6 @@
       <c r="G233" t="n">
         <v>130</v>
       </c>
-      <c r="H233" t="inlineStr"/>
       <c r="I233" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15033,7 +14801,6 @@
       <c r="G234" t="n">
         <v>130</v>
       </c>
-      <c r="H234" t="inlineStr"/>
       <c r="I234" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15090,7 +14857,6 @@
       <c r="G235" t="n">
         <v>130</v>
       </c>
-      <c r="H235" t="inlineStr"/>
       <c r="I235" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15147,7 +14913,6 @@
       <c r="G236" t="n">
         <v>130</v>
       </c>
-      <c r="H236" t="inlineStr"/>
       <c r="I236" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15204,7 +14969,6 @@
       <c r="G237" t="n">
         <v>130</v>
       </c>
-      <c r="H237" t="inlineStr"/>
       <c r="I237" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15261,7 +15025,6 @@
       <c r="G238" t="n">
         <v>130</v>
       </c>
-      <c r="H238" t="inlineStr"/>
       <c r="I238" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15318,7 +15081,6 @@
       <c r="G239" t="n">
         <v>130</v>
       </c>
-      <c r="H239" t="inlineStr"/>
       <c r="I239" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15375,7 +15137,6 @@
       <c r="G240" t="n">
         <v>220</v>
       </c>
-      <c r="H240" t="inlineStr"/>
       <c r="I240" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15432,7 +15193,6 @@
       <c r="G241" t="n">
         <v>95</v>
       </c>
-      <c r="H241" t="inlineStr"/>
       <c r="I241" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15489,7 +15249,6 @@
       <c r="G242" t="n">
         <v>95</v>
       </c>
-      <c r="H242" t="inlineStr"/>
       <c r="I242" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15546,7 +15305,6 @@
       <c r="G243" t="n">
         <v>70</v>
       </c>
-      <c r="H243" t="inlineStr"/>
       <c r="I243" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15603,7 +15361,6 @@
       <c r="G244" t="n">
         <v>70</v>
       </c>
-      <c r="H244" t="inlineStr"/>
       <c r="I244" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15660,7 +15417,6 @@
       <c r="G245" t="n">
         <v>95</v>
       </c>
-      <c r="H245" t="inlineStr"/>
       <c r="I245" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15717,7 +15473,6 @@
       <c r="G246" t="n">
         <v>95</v>
       </c>
-      <c r="H246" t="inlineStr"/>
       <c r="I246" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15774,7 +15529,6 @@
       <c r="G247" t="n">
         <v>95</v>
       </c>
-      <c r="H247" t="inlineStr"/>
       <c r="I247" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15831,7 +15585,6 @@
       <c r="G248" t="n">
         <v>95</v>
       </c>
-      <c r="H248" t="inlineStr"/>
       <c r="I248" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15888,7 +15641,6 @@
       <c r="G249" t="n">
         <v>70</v>
       </c>
-      <c r="H249" t="inlineStr"/>
       <c r="I249" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -15945,7 +15697,6 @@
       <c r="G250" t="n">
         <v>70</v>
       </c>
-      <c r="H250" t="inlineStr"/>
       <c r="I250" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16002,7 +15753,6 @@
       <c r="G251" t="n">
         <v>95</v>
       </c>
-      <c r="H251" t="inlineStr"/>
       <c r="I251" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16059,7 +15809,6 @@
       <c r="G252" t="n">
         <v>95</v>
       </c>
-      <c r="H252" t="inlineStr"/>
       <c r="I252" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16116,7 +15865,6 @@
       <c r="G253" t="n">
         <v>95</v>
       </c>
-      <c r="H253" t="inlineStr"/>
       <c r="I253" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16173,7 +15921,6 @@
       <c r="G254" t="n">
         <v>225</v>
       </c>
-      <c r="H254" t="inlineStr"/>
       <c r="I254" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16230,7 +15977,6 @@
       <c r="G255" t="n">
         <v>95</v>
       </c>
-      <c r="H255" t="inlineStr"/>
       <c r="I255" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16287,7 +16033,6 @@
       <c r="G256" t="n">
         <v>70</v>
       </c>
-      <c r="H256" t="inlineStr"/>
       <c r="I256" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16344,7 +16089,6 @@
       <c r="G257" t="n">
         <v>70</v>
       </c>
-      <c r="H257" t="inlineStr"/>
       <c r="I257" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16401,7 +16145,6 @@
       <c r="G258" t="n">
         <v>70</v>
       </c>
-      <c r="H258" t="inlineStr"/>
       <c r="I258" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16458,7 +16201,6 @@
       <c r="G259" t="n">
         <v>70</v>
       </c>
-      <c r="H259" t="inlineStr"/>
       <c r="I259" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16515,7 +16257,6 @@
       <c r="G260" t="n">
         <v>70</v>
       </c>
-      <c r="H260" t="inlineStr"/>
       <c r="I260" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16572,7 +16313,6 @@
       <c r="G261" t="n">
         <v>95</v>
       </c>
-      <c r="H261" t="inlineStr"/>
       <c r="I261" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16629,7 +16369,6 @@
       <c r="G262" t="n">
         <v>70</v>
       </c>
-      <c r="H262" t="inlineStr"/>
       <c r="I262" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16686,7 +16425,6 @@
       <c r="G263" t="n">
         <v>70</v>
       </c>
-      <c r="H263" t="inlineStr"/>
       <c r="I263" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16743,7 +16481,6 @@
       <c r="G264" t="n">
         <v>95</v>
       </c>
-      <c r="H264" t="inlineStr"/>
       <c r="I264" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16800,7 +16537,6 @@
       <c r="G265" t="n">
         <v>70</v>
       </c>
-      <c r="H265" t="inlineStr"/>
       <c r="I265" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16857,7 +16593,6 @@
       <c r="G266" t="n">
         <v>70</v>
       </c>
-      <c r="H266" t="inlineStr"/>
       <c r="I266" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16914,7 +16649,6 @@
       <c r="G267" t="n">
         <v>70</v>
       </c>
-      <c r="H267" t="inlineStr"/>
       <c r="I267" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -16971,7 +16705,6 @@
       <c r="G268" t="n">
         <v>70</v>
       </c>
-      <c r="H268" t="inlineStr"/>
       <c r="I268" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17028,7 +16761,6 @@
       <c r="G269" t="n">
         <v>225</v>
       </c>
-      <c r="H269" t="inlineStr"/>
       <c r="I269" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17085,7 +16817,6 @@
       <c r="G270" t="n">
         <v>95</v>
       </c>
-      <c r="H270" t="inlineStr"/>
       <c r="I270" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17142,7 +16873,6 @@
       <c r="G271" t="n">
         <v>95</v>
       </c>
-      <c r="H271" t="inlineStr"/>
       <c r="I271" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17199,7 +16929,6 @@
       <c r="G272" t="n">
         <v>95</v>
       </c>
-      <c r="H272" t="inlineStr"/>
       <c r="I272" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17256,7 +16985,6 @@
       <c r="G273" t="n">
         <v>95</v>
       </c>
-      <c r="H273" t="inlineStr"/>
       <c r="I273" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17313,7 +17041,6 @@
       <c r="G274" t="n">
         <v>70</v>
       </c>
-      <c r="H274" t="inlineStr"/>
       <c r="I274" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17370,7 +17097,6 @@
       <c r="G275" t="n">
         <v>95</v>
       </c>
-      <c r="H275" t="inlineStr"/>
       <c r="I275" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17427,7 +17153,6 @@
       <c r="G276" t="n">
         <v>70</v>
       </c>
-      <c r="H276" t="inlineStr"/>
       <c r="I276" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17484,7 +17209,6 @@
       <c r="G277" t="n">
         <v>70</v>
       </c>
-      <c r="H277" t="inlineStr"/>
       <c r="I277" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17541,7 +17265,6 @@
       <c r="G278" t="n">
         <v>95</v>
       </c>
-      <c r="H278" t="inlineStr"/>
       <c r="I278" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17598,7 +17321,6 @@
       <c r="G279" t="n">
         <v>45</v>
       </c>
-      <c r="H279" t="inlineStr"/>
       <c r="I279" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17655,7 +17377,6 @@
       <c r="G280" t="n">
         <v>95</v>
       </c>
-      <c r="H280" t="inlineStr"/>
       <c r="I280" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17712,7 +17433,6 @@
       <c r="G281" t="n">
         <v>95</v>
       </c>
-      <c r="H281" t="inlineStr"/>
       <c r="I281" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17769,7 +17489,6 @@
       <c r="G282" t="n">
         <v>95</v>
       </c>
-      <c r="H282" t="inlineStr"/>
       <c r="I282" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17826,7 +17545,6 @@
       <c r="G283" t="n">
         <v>70</v>
       </c>
-      <c r="H283" t="inlineStr"/>
       <c r="I283" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17883,7 +17601,6 @@
       <c r="G284" t="n">
         <v>70</v>
       </c>
-      <c r="H284" t="inlineStr"/>
       <c r="I284" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17940,7 +17657,6 @@
       <c r="G285" t="n">
         <v>95</v>
       </c>
-      <c r="H285" t="inlineStr"/>
       <c r="I285" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -17997,7 +17713,6 @@
       <c r="G286" t="n">
         <v>95</v>
       </c>
-      <c r="H286" t="inlineStr"/>
       <c r="I286" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18054,7 +17769,6 @@
       <c r="G287" t="n">
         <v>70</v>
       </c>
-      <c r="H287" t="inlineStr"/>
       <c r="I287" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18111,7 +17825,6 @@
       <c r="G288" t="n">
         <v>70</v>
       </c>
-      <c r="H288" t="inlineStr"/>
       <c r="I288" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18168,7 +17881,6 @@
       <c r="G289" t="n">
         <v>95</v>
       </c>
-      <c r="H289" t="inlineStr"/>
       <c r="I289" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18225,7 +17937,6 @@
       <c r="G290" t="n">
         <v>220</v>
       </c>
-      <c r="H290" t="inlineStr"/>
       <c r="I290" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18282,7 +17993,6 @@
       <c r="G291" t="n">
         <v>95</v>
       </c>
-      <c r="H291" t="inlineStr"/>
       <c r="I291" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18339,7 +18049,6 @@
       <c r="G292" t="n">
         <v>70</v>
       </c>
-      <c r="H292" t="inlineStr"/>
       <c r="I292" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18396,7 +18105,6 @@
       <c r="G293" t="n">
         <v>70</v>
       </c>
-      <c r="H293" t="inlineStr"/>
       <c r="I293" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18453,7 +18161,6 @@
       <c r="G294" t="n">
         <v>95</v>
       </c>
-      <c r="H294" t="inlineStr"/>
       <c r="I294" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18510,7 +18217,6 @@
       <c r="G295" t="n">
         <v>95</v>
       </c>
-      <c r="H295" t="inlineStr"/>
       <c r="I295" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18567,7 +18273,6 @@
       <c r="G296" t="n">
         <v>95</v>
       </c>
-      <c r="H296" t="inlineStr"/>
       <c r="I296" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18624,7 +18329,6 @@
       <c r="G297" t="n">
         <v>70</v>
       </c>
-      <c r="H297" t="inlineStr"/>
       <c r="I297" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18681,7 +18385,6 @@
       <c r="G298" t="n">
         <v>95</v>
       </c>
-      <c r="H298" t="inlineStr"/>
       <c r="I298" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18738,7 +18441,6 @@
       <c r="G299" t="n">
         <v>95</v>
       </c>
-      <c r="H299" t="inlineStr"/>
       <c r="I299" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18795,7 +18497,6 @@
       <c r="G300" t="n">
         <v>95</v>
       </c>
-      <c r="H300" t="inlineStr"/>
       <c r="I300" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18852,7 +18553,6 @@
       <c r="G301" t="n">
         <v>70</v>
       </c>
-      <c r="H301" t="inlineStr"/>
       <c r="I301" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18909,7 +18609,6 @@
       <c r="G302" t="n">
         <v>70</v>
       </c>
-      <c r="H302" t="inlineStr"/>
       <c r="I302" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -18966,7 +18665,6 @@
       <c r="G303" t="n">
         <v>70</v>
       </c>
-      <c r="H303" t="inlineStr"/>
       <c r="I303" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19023,7 +18721,6 @@
       <c r="G304" t="n">
         <v>70</v>
       </c>
-      <c r="H304" t="inlineStr"/>
       <c r="I304" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19080,7 +18777,6 @@
       <c r="G305" t="n">
         <v>70</v>
       </c>
-      <c r="H305" t="inlineStr"/>
       <c r="I305" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19137,7 +18833,6 @@
       <c r="G306" t="n">
         <v>70</v>
       </c>
-      <c r="H306" t="inlineStr"/>
       <c r="I306" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19194,7 +18889,6 @@
       <c r="G307" t="n">
         <v>120</v>
       </c>
-      <c r="H307" t="inlineStr"/>
       <c r="I307" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19251,7 +18945,6 @@
       <c r="G308" t="n">
         <v>120</v>
       </c>
-      <c r="H308" t="inlineStr"/>
       <c r="I308" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19308,7 +19001,6 @@
       <c r="G309" t="n">
         <v>120</v>
       </c>
-      <c r="H309" t="inlineStr"/>
       <c r="I309" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19365,7 +19057,6 @@
       <c r="G310" t="n">
         <v>210</v>
       </c>
-      <c r="H310" t="inlineStr"/>
       <c r="I310" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19422,7 +19113,6 @@
       <c r="G311" t="n">
         <v>120</v>
       </c>
-      <c r="H311" t="inlineStr"/>
       <c r="I311" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19479,7 +19169,6 @@
       <c r="G312" t="n">
         <v>120</v>
       </c>
-      <c r="H312" t="inlineStr"/>
       <c r="I312" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19536,7 +19225,6 @@
       <c r="G313" t="n">
         <v>160</v>
       </c>
-      <c r="H313" t="inlineStr"/>
       <c r="I313" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19593,7 +19281,6 @@
       <c r="G314" t="n">
         <v>160</v>
       </c>
-      <c r="H314" t="inlineStr"/>
       <c r="I314" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19650,7 +19337,6 @@
       <c r="G315" t="n">
         <v>160</v>
       </c>
-      <c r="H315" t="inlineStr"/>
       <c r="I315" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19707,7 +19393,6 @@
       <c r="G316" t="n">
         <v>160</v>
       </c>
-      <c r="H316" t="inlineStr"/>
       <c r="I316" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19740,7 +19425,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -19764,7 +19449,6 @@
       <c r="G317" t="n">
         <v>50</v>
       </c>
-      <c r="H317" t="inlineStr"/>
       <c r="I317" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19821,7 +19505,6 @@
       <c r="G318" t="n">
         <v>90</v>
       </c>
-      <c r="H318" t="inlineStr"/>
       <c r="I318" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19878,7 +19561,6 @@
       <c r="G319" t="n">
         <v>105</v>
       </c>
-      <c r="H319" t="inlineStr"/>
       <c r="I319" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19935,7 +19617,6 @@
       <c r="G320" t="n">
         <v>120</v>
       </c>
-      <c r="H320" t="inlineStr"/>
       <c r="I320" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -19992,7 +19673,6 @@
       <c r="G321" t="n">
         <v>210</v>
       </c>
-      <c r="H321" t="inlineStr"/>
       <c r="I321" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20049,7 +19729,6 @@
       <c r="G322" t="n">
         <v>120</v>
       </c>
-      <c r="H322" t="inlineStr"/>
       <c r="I322" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20106,7 +19785,6 @@
       <c r="G323" t="n">
         <v>120</v>
       </c>
-      <c r="H323" t="inlineStr"/>
       <c r="I323" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20163,7 +19841,6 @@
       <c r="G324" t="n">
         <v>120</v>
       </c>
-      <c r="H324" t="inlineStr"/>
       <c r="I324" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20220,7 +19897,6 @@
       <c r="G325" t="n">
         <v>120</v>
       </c>
-      <c r="H325" t="inlineStr"/>
       <c r="I325" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20277,7 +19953,6 @@
       <c r="G326" t="n">
         <v>120</v>
       </c>
-      <c r="H326" t="inlineStr"/>
       <c r="I326" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20334,7 +20009,6 @@
       <c r="G327" t="n">
         <v>90</v>
       </c>
-      <c r="H327" t="inlineStr"/>
       <c r="I327" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20391,7 +20065,6 @@
       <c r="G328" t="n">
         <v>90</v>
       </c>
-      <c r="H328" t="inlineStr"/>
       <c r="I328" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20448,7 +20121,6 @@
       <c r="G329" t="n">
         <v>120</v>
       </c>
-      <c r="H329" t="inlineStr"/>
       <c r="I329" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20505,7 +20177,6 @@
       <c r="G330" t="n">
         <v>210</v>
       </c>
-      <c r="H330" t="inlineStr"/>
       <c r="I330" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20562,7 +20233,6 @@
       <c r="G331" t="n">
         <v>120</v>
       </c>
-      <c r="H331" t="inlineStr"/>
       <c r="I331" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20619,7 +20289,6 @@
       <c r="G332" t="n">
         <v>120</v>
       </c>
-      <c r="H332" t="inlineStr"/>
       <c r="I332" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20676,7 +20345,6 @@
       <c r="G333" t="n">
         <v>90</v>
       </c>
-      <c r="H333" t="inlineStr"/>
       <c r="I333" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20733,7 +20401,6 @@
       <c r="G334" t="n">
         <v>160</v>
       </c>
-      <c r="H334" t="inlineStr"/>
       <c r="I334" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20790,7 +20457,6 @@
       <c r="G335" t="n">
         <v>120</v>
       </c>
-      <c r="H335" t="inlineStr"/>
       <c r="I335" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20847,7 +20513,6 @@
       <c r="G336" t="n">
         <v>120</v>
       </c>
-      <c r="H336" t="inlineStr"/>
       <c r="I336" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20904,7 +20569,6 @@
       <c r="G337" t="n">
         <v>210</v>
       </c>
-      <c r="H337" t="inlineStr"/>
       <c r="I337" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20937,7 +20601,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -20961,7 +20625,6 @@
       <c r="G338" t="n">
         <v>50</v>
       </c>
-      <c r="H338" t="inlineStr"/>
       <c r="I338" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -20994,7 +20657,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -21018,7 +20681,6 @@
       <c r="G339" t="n">
         <v>50</v>
       </c>
-      <c r="H339" t="inlineStr"/>
       <c r="I339" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21051,7 +20713,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -21075,7 +20737,6 @@
       <c r="G340" t="n">
         <v>50</v>
       </c>
-      <c r="H340" t="inlineStr"/>
       <c r="I340" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21108,7 +20769,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -21132,7 +20793,6 @@
       <c r="G341" t="n">
         <v>50</v>
       </c>
-      <c r="H341" t="inlineStr"/>
       <c r="I341" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21189,7 +20849,6 @@
       <c r="G342" t="n">
         <v>90</v>
       </c>
-      <c r="H342" t="inlineStr"/>
       <c r="I342" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21222,7 +20881,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -21246,7 +20905,6 @@
       <c r="G343" t="n">
         <v>50</v>
       </c>
-      <c r="H343" t="inlineStr"/>
       <c r="I343" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21303,7 +20961,6 @@
       <c r="G344" t="n">
         <v>80</v>
       </c>
-      <c r="H344" t="inlineStr"/>
       <c r="I344" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21360,7 +21017,6 @@
       <c r="G345" t="n">
         <v>90</v>
       </c>
-      <c r="H345" t="inlineStr"/>
       <c r="I345" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21393,7 +21049,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -21417,7 +21073,6 @@
       <c r="G346" t="n">
         <v>50</v>
       </c>
-      <c r="H346" t="inlineStr"/>
       <c r="I346" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21474,7 +21129,6 @@
       <c r="G347" t="n">
         <v>90</v>
       </c>
-      <c r="H347" t="inlineStr"/>
       <c r="I347" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21531,7 +21185,6 @@
       <c r="G348" t="n">
         <v>80</v>
       </c>
-      <c r="H348" t="inlineStr"/>
       <c r="I348" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21588,7 +21241,6 @@
       <c r="G349" t="n">
         <v>150</v>
       </c>
-      <c r="H349" t="inlineStr"/>
       <c r="I349" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21645,7 +21297,6 @@
       <c r="G350" t="n">
         <v>90</v>
       </c>
-      <c r="H350" t="inlineStr"/>
       <c r="I350" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21702,7 +21353,6 @@
       <c r="G351" t="n">
         <v>90</v>
       </c>
-      <c r="H351" t="inlineStr"/>
       <c r="I351" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21759,7 +21409,6 @@
       <c r="G352" t="n">
         <v>90</v>
       </c>
-      <c r="H352" t="inlineStr"/>
       <c r="I352" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21816,7 +21465,6 @@
       <c r="G353" t="n">
         <v>105</v>
       </c>
-      <c r="H353" t="inlineStr"/>
       <c r="I353" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21849,7 +21497,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -21873,7 +21521,6 @@
       <c r="G354" t="n">
         <v>50</v>
       </c>
-      <c r="H354" t="inlineStr"/>
       <c r="I354" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21906,7 +21553,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -21930,7 +21577,6 @@
       <c r="G355" t="n">
         <v>50</v>
       </c>
-      <c r="H355" t="inlineStr"/>
       <c r="I355" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -21963,7 +21609,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -21987,7 +21633,6 @@
       <c r="G356" t="n">
         <v>50</v>
       </c>
-      <c r="H356" t="inlineStr"/>
       <c r="I356" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22020,7 +21665,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -22044,7 +21689,6 @@
       <c r="G357" t="n">
         <v>50</v>
       </c>
-      <c r="H357" t="inlineStr"/>
       <c r="I357" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22077,7 +21721,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -22101,7 +21745,6 @@
       <c r="G358" t="n">
         <v>50</v>
       </c>
-      <c r="H358" t="inlineStr"/>
       <c r="I358" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22134,7 +21777,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -22158,7 +21801,6 @@
       <c r="G359" t="n">
         <v>50</v>
       </c>
-      <c r="H359" t="inlineStr"/>
       <c r="I359" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22215,7 +21857,6 @@
       <c r="G360" t="n">
         <v>90</v>
       </c>
-      <c r="H360" t="inlineStr"/>
       <c r="I360" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22248,7 +21889,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -22272,7 +21913,6 @@
       <c r="G361" t="n">
         <v>50</v>
       </c>
-      <c r="H361" t="inlineStr"/>
       <c r="I361" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22305,7 +21945,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -22329,7 +21969,6 @@
       <c r="G362" t="n">
         <v>50</v>
       </c>
-      <c r="H362" t="inlineStr"/>
       <c r="I362" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22362,7 +22001,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -22386,7 +22025,6 @@
       <c r="G363" t="n">
         <v>50</v>
       </c>
-      <c r="H363" t="inlineStr"/>
       <c r="I363" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22419,7 +22057,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -22443,7 +22081,6 @@
       <c r="G364" t="n">
         <v>50</v>
       </c>
-      <c r="H364" t="inlineStr"/>
       <c r="I364" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22476,7 +22113,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -22500,7 +22137,6 @@
       <c r="G365" t="n">
         <v>50</v>
       </c>
-      <c r="H365" t="inlineStr"/>
       <c r="I365" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22557,7 +22193,6 @@
       <c r="G366" t="n">
         <v>90</v>
       </c>
-      <c r="H366" t="inlineStr"/>
       <c r="I366" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22614,7 +22249,6 @@
       <c r="G367" t="n">
         <v>80</v>
       </c>
-      <c r="H367" t="inlineStr"/>
       <c r="I367" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22671,7 +22305,6 @@
       <c r="G368" t="n">
         <v>210</v>
       </c>
-      <c r="H368" t="inlineStr"/>
       <c r="I368" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22728,7 +22361,6 @@
       <c r="G369" t="n">
         <v>210</v>
       </c>
-      <c r="H369" t="inlineStr"/>
       <c r="I369" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22785,7 +22417,6 @@
       <c r="G370" t="n">
         <v>120</v>
       </c>
-      <c r="H370" t="inlineStr"/>
       <c r="I370" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22842,7 +22473,6 @@
       <c r="G371" t="n">
         <v>120</v>
       </c>
-      <c r="H371" t="inlineStr"/>
       <c r="I371" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22899,7 +22529,6 @@
       <c r="G372" t="n">
         <v>120</v>
       </c>
-      <c r="H372" t="inlineStr"/>
       <c r="I372" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22956,7 +22585,6 @@
       <c r="G373" t="n">
         <v>80</v>
       </c>
-      <c r="H373" t="inlineStr"/>
       <c r="I373" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -22989,7 +22617,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -23013,7 +22641,6 @@
       <c r="G374" t="n">
         <v>50</v>
       </c>
-      <c r="H374" t="inlineStr"/>
       <c r="I374" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23046,7 +22673,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -23070,7 +22697,6 @@
       <c r="G375" t="n">
         <v>50</v>
       </c>
-      <c r="H375" t="inlineStr"/>
       <c r="I375" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23127,7 +22753,6 @@
       <c r="G376" t="n">
         <v>80</v>
       </c>
-      <c r="H376" t="inlineStr"/>
       <c r="I376" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23184,7 +22809,6 @@
       <c r="G377" t="n">
         <v>80</v>
       </c>
-      <c r="H377" t="inlineStr"/>
       <c r="I377" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23241,7 +22865,6 @@
       <c r="G378" t="n">
         <v>80</v>
       </c>
-      <c r="H378" t="inlineStr"/>
       <c r="I378" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23274,7 +22897,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -23298,7 +22921,6 @@
       <c r="G379" t="n">
         <v>50</v>
       </c>
-      <c r="H379" t="inlineStr"/>
       <c r="I379" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23355,7 +22977,6 @@
       <c r="G380" t="n">
         <v>90</v>
       </c>
-      <c r="H380" t="inlineStr"/>
       <c r="I380" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23412,7 +23033,6 @@
       <c r="G381" t="n">
         <v>90</v>
       </c>
-      <c r="H381" t="inlineStr"/>
       <c r="I381" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23469,7 +23089,6 @@
       <c r="G382" t="n">
         <v>90</v>
       </c>
-      <c r="H382" t="inlineStr"/>
       <c r="I382" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23526,7 +23145,6 @@
       <c r="G383" t="n">
         <v>120</v>
       </c>
-      <c r="H383" t="inlineStr"/>
       <c r="I383" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23583,7 +23201,6 @@
       <c r="G384" t="n">
         <v>210</v>
       </c>
-      <c r="H384" t="inlineStr"/>
       <c r="I384" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23640,7 +23257,6 @@
       <c r="G385" t="n">
         <v>120</v>
       </c>
-      <c r="H385" t="inlineStr"/>
       <c r="I385" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23697,7 +23313,6 @@
       <c r="G386" t="n">
         <v>160</v>
       </c>
-      <c r="H386" t="inlineStr"/>
       <c r="I386" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23730,7 +23345,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -23754,7 +23369,6 @@
       <c r="G387" t="n">
         <v>50</v>
       </c>
-      <c r="H387" t="inlineStr"/>
       <c r="I387" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23787,7 +23401,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -23811,7 +23425,6 @@
       <c r="G388" t="n">
         <v>50</v>
       </c>
-      <c r="H388" t="inlineStr"/>
       <c r="I388" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23844,7 +23457,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -23868,7 +23481,6 @@
       <c r="G389" t="n">
         <v>50</v>
       </c>
-      <c r="H389" t="inlineStr"/>
       <c r="I389" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23901,7 +23513,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -23925,7 +23537,6 @@
       <c r="G390" t="n">
         <v>50</v>
       </c>
-      <c r="H390" t="inlineStr"/>
       <c r="I390" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -23982,7 +23593,6 @@
       <c r="G391" t="n">
         <v>210</v>
       </c>
-      <c r="H391" t="inlineStr"/>
       <c r="I391" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24039,7 +23649,6 @@
       <c r="G392" t="n">
         <v>210</v>
       </c>
-      <c r="H392" t="inlineStr"/>
       <c r="I392" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24096,7 +23705,6 @@
       <c r="G393" t="n">
         <v>160</v>
       </c>
-      <c r="H393" t="inlineStr"/>
       <c r="I393" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24153,7 +23761,6 @@
       <c r="G394" t="n">
         <v>210</v>
       </c>
-      <c r="H394" t="inlineStr"/>
       <c r="I394" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24210,7 +23817,6 @@
       <c r="G395" t="n">
         <v>160</v>
       </c>
-      <c r="H395" t="inlineStr"/>
       <c r="I395" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24267,7 +23873,6 @@
       <c r="G396" t="n">
         <v>90</v>
       </c>
-      <c r="H396" t="inlineStr"/>
       <c r="I396" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24300,7 +23905,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -24324,7 +23929,6 @@
       <c r="G397" t="n">
         <v>50</v>
       </c>
-      <c r="H397" t="inlineStr"/>
       <c r="I397" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24357,7 +23961,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -24381,7 +23985,6 @@
       <c r="G398" t="n">
         <v>50</v>
       </c>
-      <c r="H398" t="inlineStr"/>
       <c r="I398" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24438,7 +24041,6 @@
       <c r="G399" t="n">
         <v>90</v>
       </c>
-      <c r="H399" t="inlineStr"/>
       <c r="I399" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24471,7 +24073,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -24495,7 +24097,6 @@
       <c r="G400" t="n">
         <v>50</v>
       </c>
-      <c r="H400" t="inlineStr"/>
       <c r="I400" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24552,7 +24153,6 @@
       <c r="G401" t="n">
         <v>90</v>
       </c>
-      <c r="H401" t="inlineStr"/>
       <c r="I401" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24585,7 +24185,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -24609,7 +24209,6 @@
       <c r="G402" t="n">
         <v>50</v>
       </c>
-      <c r="H402" t="inlineStr"/>
       <c r="I402" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24666,7 +24265,6 @@
       <c r="G403" t="n">
         <v>80</v>
       </c>
-      <c r="H403" t="inlineStr"/>
       <c r="I403" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24723,7 +24321,6 @@
       <c r="G404" t="n">
         <v>110</v>
       </c>
-      <c r="H404" t="inlineStr"/>
       <c r="I404" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24756,7 +24353,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -24780,7 +24377,6 @@
       <c r="G405" t="n">
         <v>50</v>
       </c>
-      <c r="H405" t="inlineStr"/>
       <c r="I405" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24813,7 +24409,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -24837,7 +24433,6 @@
       <c r="G406" t="n">
         <v>50</v>
       </c>
-      <c r="H406" t="inlineStr"/>
       <c r="I406" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24870,7 +24465,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -24894,7 +24489,6 @@
       <c r="G407" t="n">
         <v>50</v>
       </c>
-      <c r="H407" t="inlineStr"/>
       <c r="I407" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -24951,7 +24545,6 @@
       <c r="G408" t="n">
         <v>210</v>
       </c>
-      <c r="H408" t="inlineStr"/>
       <c r="I408" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25008,7 +24601,6 @@
       <c r="G409" t="n">
         <v>90</v>
       </c>
-      <c r="H409" t="inlineStr"/>
       <c r="I409" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25065,7 +24657,6 @@
       <c r="G410" t="n">
         <v>90</v>
       </c>
-      <c r="H410" t="inlineStr"/>
       <c r="I410" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25122,7 +24713,6 @@
       <c r="G411" t="n">
         <v>80</v>
       </c>
-      <c r="H411" t="inlineStr"/>
       <c r="I411" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25179,7 +24769,6 @@
       <c r="G412" t="n">
         <v>95</v>
       </c>
-      <c r="H412" t="inlineStr"/>
       <c r="I412" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25236,7 +24825,6 @@
       <c r="G413" t="n">
         <v>95</v>
       </c>
-      <c r="H413" t="inlineStr"/>
       <c r="I413" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25269,7 +24857,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -25293,7 +24881,6 @@
       <c r="G414" t="n">
         <v>60</v>
       </c>
-      <c r="H414" t="inlineStr"/>
       <c r="I414" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25326,7 +24913,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>Studio</t>
+          <t>Apartment</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -25350,7 +24937,6 @@
       <c r="G415" t="n">
         <v>60</v>
       </c>
-      <c r="H415" t="inlineStr"/>
       <c r="I415" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25407,7 +24993,6 @@
       <c r="G416" t="n">
         <v>100</v>
       </c>
-      <c r="H416" t="inlineStr"/>
       <c r="I416" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25464,7 +25049,6 @@
       <c r="G417" t="n">
         <v>120</v>
       </c>
-      <c r="H417" t="inlineStr"/>
       <c r="I417" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25521,7 +25105,6 @@
       <c r="G418" t="n">
         <v>90</v>
       </c>
-      <c r="H418" t="inlineStr"/>
       <c r="I418" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25578,7 +25161,6 @@
       <c r="G419" t="n">
         <v>95</v>
       </c>
-      <c r="H419" t="inlineStr"/>
       <c r="I419" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25635,7 +25217,6 @@
       <c r="G420" t="n">
         <v>90</v>
       </c>
-      <c r="H420" t="inlineStr"/>
       <c r="I420" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25692,7 +25273,6 @@
       <c r="G421" t="n">
         <v>90</v>
       </c>
-      <c r="H421" t="inlineStr"/>
       <c r="I421" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25749,7 +25329,6 @@
       <c r="G422" t="n">
         <v>90</v>
       </c>
-      <c r="H422" t="inlineStr"/>
       <c r="I422" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25806,7 +25385,6 @@
       <c r="G423" t="n">
         <v>90</v>
       </c>
-      <c r="H423" t="inlineStr"/>
       <c r="I423" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25863,7 +25441,6 @@
       <c r="G424" t="n">
         <v>90</v>
       </c>
-      <c r="H424" t="inlineStr"/>
       <c r="I424" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25920,7 +25497,6 @@
       <c r="G425" t="n">
         <v>415</v>
       </c>
-      <c r="H425" t="inlineStr"/>
       <c r="I425" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -25977,7 +25553,6 @@
       <c r="G426" t="n">
         <v>415</v>
       </c>
-      <c r="H426" t="inlineStr"/>
       <c r="I426" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26034,7 +25609,6 @@
       <c r="G427" t="n">
         <v>120</v>
       </c>
-      <c r="H427" t="inlineStr"/>
       <c r="I427" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26091,7 +25665,6 @@
       <c r="G428" t="n">
         <v>90</v>
       </c>
-      <c r="H428" t="inlineStr"/>
       <c r="I428" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26148,7 +25721,6 @@
       <c r="G429" t="n">
         <v>90</v>
       </c>
-      <c r="H429" t="inlineStr"/>
       <c r="I429" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26205,7 +25777,6 @@
       <c r="G430" t="n">
         <v>120</v>
       </c>
-      <c r="H430" t="inlineStr"/>
       <c r="I430" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26262,7 +25833,6 @@
       <c r="G431" t="n">
         <v>115</v>
       </c>
-      <c r="H431" t="inlineStr"/>
       <c r="I431" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26295,7 +25865,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -26319,7 +25889,6 @@
       <c r="G432" t="n">
         <v>446</v>
       </c>
-      <c r="H432" t="inlineStr"/>
       <c r="I432" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26352,7 +25921,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -26376,7 +25945,6 @@
       <c r="G433" t="n">
         <v>248</v>
       </c>
-      <c r="H433" t="inlineStr"/>
       <c r="I433" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26409,7 +25977,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -26433,7 +26001,6 @@
       <c r="G434" t="n">
         <v>288</v>
       </c>
-      <c r="H434" t="inlineStr"/>
       <c r="I434" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26490,7 +26057,6 @@
       <c r="G435" t="n">
         <v>175</v>
       </c>
-      <c r="H435" t="inlineStr"/>
       <c r="I435" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26547,7 +26113,6 @@
       <c r="G436" t="n">
         <v>175</v>
       </c>
-      <c r="H436" t="inlineStr"/>
       <c r="I436" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26580,7 +26145,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Villa</t>
+          <t>Standalone Villa</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -26604,7 +26169,6 @@
       <c r="G437" t="n">
         <v>263</v>
       </c>
-      <c r="H437" t="inlineStr"/>
       <c r="I437" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26661,7 +26225,6 @@
       <c r="G438" t="n">
         <v>200</v>
       </c>
-      <c r="H438" t="inlineStr"/>
       <c r="I438" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26718,7 +26281,6 @@
       <c r="G439" t="n">
         <v>102</v>
       </c>
-      <c r="H439" t="inlineStr"/>
       <c r="I439" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26775,7 +26337,6 @@
       <c r="G440" t="n">
         <v>100</v>
       </c>
-      <c r="H440" t="inlineStr"/>
       <c r="I440" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26832,7 +26393,6 @@
       <c r="G441" t="n">
         <v>102</v>
       </c>
-      <c r="H441" t="inlineStr"/>
       <c r="I441" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26889,7 +26449,6 @@
       <c r="G442" t="n">
         <v>100</v>
       </c>
-      <c r="H442" t="inlineStr"/>
       <c r="I442" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -26946,7 +26505,6 @@
       <c r="G443" t="n">
         <v>119</v>
       </c>
-      <c r="H443" t="inlineStr"/>
       <c r="I443" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -27003,7 +26561,6 @@
       <c r="G444" t="n">
         <v>115</v>
       </c>
-      <c r="H444" t="inlineStr"/>
       <c r="I444" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -27060,7 +26617,6 @@
       <c r="G445" t="n">
         <v>102</v>
       </c>
-      <c r="H445" t="inlineStr"/>
       <c r="I445" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -27117,7 +26673,6 @@
       <c r="G446" t="n">
         <v>100</v>
       </c>
-      <c r="H446" t="inlineStr"/>
       <c r="I446" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -27174,7 +26729,6 @@
       <c r="G447" t="n">
         <v>115</v>
       </c>
-      <c r="H447" t="inlineStr"/>
       <c r="I447" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -27231,7 +26785,6 @@
       <c r="G448" t="n">
         <v>119</v>
       </c>
-      <c r="H448" t="inlineStr"/>
       <c r="I448" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -27288,7 +26841,6 @@
       <c r="G449" t="n">
         <v>115</v>
       </c>
-      <c r="H449" t="inlineStr"/>
       <c r="I449" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -27345,7 +26897,6 @@
       <c r="G450" t="n">
         <v>102</v>
       </c>
-      <c r="H450" t="inlineStr"/>
       <c r="I450" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -27402,7 +26953,6 @@
       <c r="G451" t="n">
         <v>102</v>
       </c>
-      <c r="H451" t="inlineStr"/>
       <c r="I451" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -27459,7 +27009,6 @@
       <c r="G452" t="n">
         <v>119</v>
       </c>
-      <c r="H452" t="inlineStr"/>
       <c r="I452" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -27516,7 +27065,6 @@
       <c r="G453" t="n">
         <v>115</v>
       </c>
-      <c r="H453" t="inlineStr"/>
       <c r="I453" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -27573,7 +27121,6 @@
       <c r="G454" t="n">
         <v>79</v>
       </c>
-      <c r="H454" t="inlineStr"/>
       <c r="I454" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -27630,7 +27177,6 @@
       <c r="G455" t="n">
         <v>75</v>
       </c>
-      <c r="H455" t="inlineStr"/>
       <c r="I455" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -27687,7 +27233,6 @@
       <c r="G456" t="n">
         <v>119</v>
       </c>
-      <c r="H456" t="inlineStr"/>
       <c r="I456" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -27744,7 +27289,6 @@
       <c r="G457" t="n">
         <v>65</v>
       </c>
-      <c r="H457" t="inlineStr"/>
       <c r="I457" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -27801,7 +27345,6 @@
       <c r="G458" t="n">
         <v>102</v>
       </c>
-      <c r="H458" t="inlineStr"/>
       <c r="I458" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -27858,7 +27401,6 @@
       <c r="G459" t="n">
         <v>102</v>
       </c>
-      <c r="H459" t="inlineStr"/>
       <c r="I459" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -27915,7 +27457,6 @@
       <c r="G460" t="n">
         <v>75</v>
       </c>
-      <c r="H460" t="inlineStr"/>
       <c r="I460" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -27972,7 +27513,6 @@
       <c r="G461" t="n">
         <v>119</v>
       </c>
-      <c r="H461" t="inlineStr"/>
       <c r="I461" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -28029,7 +27569,6 @@
       <c r="G462" t="n">
         <v>65</v>
       </c>
-      <c r="H462" t="inlineStr"/>
       <c r="I462" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -28086,7 +27625,6 @@
       <c r="G463" t="n">
         <v>75</v>
       </c>
-      <c r="H463" t="inlineStr"/>
       <c r="I463" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -28143,7 +27681,6 @@
       <c r="G464" t="n">
         <v>65</v>
       </c>
-      <c r="H464" t="inlineStr"/>
       <c r="I464" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -28200,7 +27737,6 @@
       <c r="G465" t="n">
         <v>102</v>
       </c>
-      <c r="H465" t="inlineStr"/>
       <c r="I465" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -28257,7 +27793,6 @@
       <c r="G466" t="n">
         <v>75</v>
       </c>
-      <c r="H466" t="inlineStr"/>
       <c r="I466" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -28314,7 +27849,6 @@
       <c r="G467" t="n">
         <v>75</v>
       </c>
-      <c r="H467" t="inlineStr"/>
       <c r="I467" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -28371,7 +27905,6 @@
       <c r="G468" t="n">
         <v>117</v>
       </c>
-      <c r="H468" t="inlineStr"/>
       <c r="I468" t="inlineStr">
         <is>
           <t>Landscape</t>
@@ -28428,7 +27961,6 @@
       <c r="G469" t="n">
         <v>139</v>
       </c>
-      <c r="H469" t="inlineStr"/>
       <c r="I469" t="inlineStr">
         <is>
           <t>Landscape</t>
